--- a/outputs/D_borderless.xlsx
+++ b/outputs/D_borderless.xlsx
@@ -10,25 +10,27 @@
     <sheet name="Data 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Validation Report" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Page Audit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Read me" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cell Evidence" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Verification" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Constraints" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Repair Proposals" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Correction History" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Join Receipt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Read me" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cell Evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Verification" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Constraints" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Repair Proposals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Correction History" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$L$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$613</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Correction History'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$M$613</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3570,6 +3572,79 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Excel row</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Supporting equations</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -4063,7 +4138,7 @@
         <v>0.92</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>0.099</v>
+        <v>0.336</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -4105,7 +4180,7 @@
         <v>0.92</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>0.409</v>
+        <v>0.946</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -4147,7 +4222,7 @@
         <v>0.92</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>0.111</v>
+        <v>0.27</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -4189,7 +4264,7 @@
         <v>0.92</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>0.189</v>
+        <v>0.311</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -4231,7 +4306,7 @@
         <v>0.92</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0.321</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -4273,7 +4348,7 @@
         <v>0.92</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.126</v>
+        <v>0.269</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -4315,7 +4390,7 @@
         <v>0.92</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.198</v>
+        <v>0.302</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -4357,7 +4432,7 @@
         <v>0.92</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.32</v>
+        <v>0.959</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -4399,7 +4474,7 @@
         <v>0.92</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.068</v>
+        <v>0.267</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -4430,6 +4505,163 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source pages</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Page joins</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Repeated headers removed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Split rows recovered</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PDF page</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source rows on page</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Output rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5486,7 +5718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5530,7 +5762,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>2.346</v>
+        <v>6.079</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -5659,7 +5891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33296,7 +33528,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33341,7 +33573,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>6dcc517ff90f59afa6ddfe780d045b33acf2e0f8ab30dad5d90915602b89ae67</t>
+          <t>5af7b2ffb8329012c3d91c50c4de4bfbd48afc9b5404ee842b3ef531ee0c38bd</t>
         </is>
       </c>
     </row>
@@ -33443,7 +33675,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33540,77 +33772,4 @@
   <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Excel row</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Supporting equations</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>